--- a/modele_deterministe/donnees.xlsx
+++ b/modele_deterministe/donnees.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06456AB2-C89E-45E0-A340-42CD3C879770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE97ECF2-198E-46EB-A8C0-A4627B7EE8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="794" activeTab="4" xr2:uid="{087A1B5B-7B97-4327-AC94-7D0ECF997B43}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="794" xr2:uid="{087A1B5B-7B97-4327-AC94-7D0ECF997B43}"/>
   </bookViews>
   <sheets>
     <sheet name="Approche déterministe" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="42">
   <si>
     <t>Demande</t>
   </si>
@@ -133,6 +133,36 @@
   </si>
   <si>
     <t>Probabilite</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -170,7 +200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -548,6 +578,17 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -597,7 +638,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1113,7 +1154,7 @@
       </c>
       <c r="C23" s="34"/>
       <c r="D23" s="12">
-        <v>0.2</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
@@ -1149,15 +1190,15 @@
       <c r="C27" s="23"/>
       <c r="D27" s="1">
         <f>C28</f>
-        <v>6.324555320336759</v>
+        <v>17.392527130926087</v>
       </c>
       <c r="E27" s="1">
         <f>C29</f>
-        <v>17.204650534085257</v>
+        <v>47.312788968734452</v>
       </c>
       <c r="F27" s="3">
         <f>C30</f>
-        <v>14.560219778561038</v>
+        <v>40.040604391042855</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
@@ -1166,16 +1207,16 @@
       </c>
       <c r="C28" s="1">
         <f>(SQRT((C12-C11)^2 + (D12-D11)^2))*D23</f>
-        <v>6.324555320336759</v>
+        <v>17.392527130926087</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="1">
         <f>D29</f>
-        <v>11.313708498984761</v>
+        <v>31.112698372208094</v>
       </c>
       <c r="F28" s="3">
         <f>D30</f>
-        <v>12.16552506059644</v>
+        <v>33.455193916640212</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
@@ -1184,16 +1225,16 @@
       </c>
       <c r="C29" s="1">
         <f>(SQRT((C13-C11)^2 + (D13-D11)^2))*D23</f>
-        <v>17.204650534085257</v>
+        <v>47.312788968734452</v>
       </c>
       <c r="D29" s="1">
         <f>(SQRT((C13-C12)^2 + (D13-D12)^2))*D23</f>
-        <v>11.313708498984761</v>
+        <v>31.112698372208094</v>
       </c>
       <c r="E29" s="23"/>
       <c r="F29" s="3">
         <f>E30</f>
-        <v>10.770329614269009</v>
+        <v>29.618406439239774</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
@@ -1202,15 +1243,15 @@
       </c>
       <c r="C30" s="5">
         <f>(SQRT((C14-C11)^2 + (D14-D11)^2))*D23</f>
-        <v>14.560219778561038</v>
+        <v>40.040604391042855</v>
       </c>
       <c r="D30" s="5">
         <f>(SQRT((C14-C12)^2 + (D14-D12)^2))*D23</f>
-        <v>12.16552506059644</v>
+        <v>33.455193916640212</v>
       </c>
       <c r="E30" s="5">
         <f>(SQRT((C14-C13)^2 + (D14-D13)^2))*D23</f>
-        <v>10.770329614269009</v>
+        <v>29.618406439239774</v>
       </c>
       <c r="F30" s="24"/>
     </row>
@@ -1260,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E7AEEC9-353D-473A-9ADB-652C7A77150E}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.44140625" customWidth="1"/>
@@ -1420,6 +1461,372 @@
         <f>'Approche déterministe'!E7</f>
         <v>2</v>
       </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="36"/>
+      <c r="B44" s="26"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="36"/>
+      <c r="B45" s="26"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="36"/>
+      <c r="B46" s="26"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="36"/>
+      <c r="B47" s="26"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="36"/>
+      <c r="B48" s="26"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="36"/>
+      <c r="B49" s="26"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B50" s="26"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="26"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="26"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B53" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1448,7 +1855,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="9">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1456,7 +1863,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1464,7 +1871,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="6">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1901,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1502,7 +1909,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1510,7 +1917,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="6">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1520,7 +1927,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F16090-0968-47E1-8D71-17427DA9CED4}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1562,7 +1969,7 @@
         <v>70</v>
       </c>
       <c r="D3" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1576,7 +1983,7 @@
         <v>30</v>
       </c>
       <c r="D4" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1590,7 +1997,147 @@
         <v>10</v>
       </c>
       <c r="D5" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>60</v>
+      </c>
+      <c r="D10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>90</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>85</v>
+      </c>
+      <c r="D13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>40</v>
+      </c>
+      <c r="B14">
+        <v>15</v>
+      </c>
+      <c r="C14">
+        <v>55</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15">
+        <v>19</v>
+      </c>
+      <c r="C15">
+        <v>75</v>
+      </c>
+      <c r="D15">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1600,10 +2147,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67873F19-09DB-4B30-B661-24661F264597}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1619,93 +2166,144 @@
       <c r="E1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="36"/>
       <c r="C2">
-        <f>B3</f>
-        <v>3.1622776601683795</v>
+        <v>17.392527130926087</v>
       </c>
       <c r="D2">
-        <f>B4</f>
-        <v>8.6023252670426285</v>
+        <v>47.312788968734452</v>
       </c>
       <c r="E2">
-        <f>B5</f>
-        <v>7.2801098892805189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>40.040604391042855</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <f>(SQRT((capacite!B3-capacite!$B$2)^2 + (capacite!C3-capacite!$C$2)^2))*cout_transport!$C$8</f>
-        <v>3.1622776601683795</v>
-      </c>
-      <c r="C3" s="36"/>
+        <v>17.392527130926087</v>
+      </c>
       <c r="D3">
-        <f>C4</f>
-        <v>5.6568542494923806</v>
+        <v>31.112698372208094</v>
       </c>
       <c r="E3">
-        <f>C5</f>
-        <v>6.0827625302982202</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33.455193916640212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <f>(SQRT((capacite!B4-capacite!$B$2)^2 + (capacite!C4-capacite!$C$2)^2))*cout_transport!$C$8</f>
-        <v>8.6023252670426285</v>
+        <v>47.312788968734452</v>
       </c>
       <c r="C4">
-        <f>(SQRT((capacite!B4-capacite!$B$3)^2 + (capacite!C4-capacite!$C$3)^2))*$C$8</f>
-        <v>5.6568542494923806</v>
-      </c>
-      <c r="D4" s="36"/>
+        <v>31.112698372208094</v>
+      </c>
       <c r="E4">
-        <f>D5</f>
-        <v>5.3851648071345046</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29.618406439239774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <f>(SQRT((capacite!B5-capacite!$B$2)^2 + (capacite!C5-capacite!$C$2)^2))*cout_transport!$C$8</f>
-        <v>7.2801098892805189</v>
+        <v>40.040604391042898</v>
       </c>
       <c r="C5">
-        <f>(SQRT((capacite!B5-capacite!$B$3)^2 + (capacite!C5-capacite!$C$3)^2))*$C$8</f>
-        <v>6.0827625302982202</v>
+        <v>33.455193916640212</v>
       </c>
       <c r="D5">
-        <f>(SQRT((capacite!B5-capacite!$B$4)^2 + (capacite!C5-capacite!$C$4)^2))*$C$8</f>
-        <v>5.3851648071345046</v>
-      </c>
-      <c r="E5" s="36"/>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="12">
-        <v>0.1</v>
+        <v>29.618406439239774</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A8:B8"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
